--- a/public/downloads/normal.xlsx
+++ b/public/downloads/normal.xlsx
@@ -1260,14 +1260,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="华文楷体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <u/>
       <sz val="14"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="华文楷体"/>
       <charset val="134"/>
     </font>
